--- a/docs/downloads/11/tbl_cata_type_alaotra_avaradrano.xlsx
+++ b/docs/downloads/11/tbl_cata_type_alaotra_avaradrano.xlsx
@@ -531,12 +531,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +543,6 @@
           <t>Criquets</t>
         </is>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -567,12 +555,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -585,12 +567,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -765,12 +741,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -783,12 +753,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -800,12 +764,6 @@
         <is>
           <t>Criquets</t>
         </is>
-      </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>0.4</v>
       </c>
     </row>
   </sheetData>
